--- a/output/full_scan/batch_seq5_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq5_2026-06-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -792,21 +792,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5515</v>
+        <v>4807</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>建國</t>
+          <t>日成-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>721.2226865452039</v>
+        <v>728.6979283415221</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>72.41484482861502</v>
+        <v>78.87395670961052</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21.92526496100084</v>
+        <v>60.97670294712506</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.122268654520396</v>
+        <v>0.8697928341522182</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2858163417093992</v>
+        <v>0.8098063286947532</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4306</v>
+        <v>5515</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>炎洲</t>
+          <t>建國</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>711.4653144466905</v>
+        <v>721.2226865452039</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16.1</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>85.80018825890907</v>
+        <v>72.41484482861502</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>42.15380473970585</v>
+        <v>21.92526496100084</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.14653144466905</v>
+        <v>1.122268654520396</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1706262014314863</v>
+        <v>0.2858163417093992</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4739</v>
+        <v>4306</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>康普</t>
+          <t>炎洲</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>704.1493567368813</v>
+        <v>711.4653144466905</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>121.5</v>
+        <v>16.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.04236510170628</v>
+        <v>85.80018825890907</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>31.66664098125847</v>
+        <v>42.15380473970585</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.914935673688124</v>
+        <v>2.14653144466905</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.134874832793771</v>
+        <v>0.1706262014314863</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6156</v>
+        <v>4739</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>松上</t>
+          <t>康普</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>690.1591685477355</v>
+        <v>704.1493567368813</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>20.55</v>
+        <v>121.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.94274561283981</v>
+        <v>64.04236510170628</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13.47732478413917</v>
+        <v>31.66664098125847</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.515916854773552</v>
+        <v>0.914935673688124</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1866887489174329</v>
+        <v>1.134874832793771</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6024</v>
+        <v>6116</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>群益期</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>678.7437458119672</v>
+        <v>701.8311289590233</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>61.5</v>
+        <v>15.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>71.48599785037244</v>
+        <v>54.3264977807434</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27.22838088859302</v>
+        <v>40.36346779290179</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8743745811967143</v>
+        <v>0.1831128959023278</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.3035027811658151</v>
+        <v>-0.4855556943652317</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5534</v>
+        <v>6156</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>長虹</t>
+          <t>松上</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>670.6661495311389</v>
+        <v>690.1591685477355</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>20.55</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>69.86792683166777</v>
+        <v>60.94274561283981</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.00749278249691</v>
+        <v>13.47732478413917</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.566614953113895</v>
+        <v>3.515916854773552</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.08881519327225</v>
+        <v>0.1866887489174329</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5880</v>
+        <v>6024</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>群益期</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>664.9119214580296</v>
+        <v>678.7437458119672</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24.05</v>
+        <v>61.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>66.94831592516239</v>
+        <v>71.48599785037244</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.83008876309358</v>
+        <v>27.22838088859302</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.9911921458029664</v>
+        <v>0.8743745811967143</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1326436317656008</v>
+        <v>0.3035027811658151</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5871</v>
+        <v>5534</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>長虹</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>651.8740960686548</v>
+        <v>670.6661495311389</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>121.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>64.43053422146244</v>
+        <v>69.86792683166777</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>21.67158100638257</v>
+        <v>31.00749278249691</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6874096068654809</v>
+        <v>1.566614953113895</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.263013932495586</v>
+        <v>1.08881519327225</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5288</v>
+        <v>5880</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>豐祥-KY</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>651.6436885278916</v>
+        <v>664.9119214580296</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>190.5</v>
+        <v>24.05</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>80.09878817280384</v>
+        <v>66.94831592516239</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.81852206844126</v>
+        <v>29.83008876309358</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.164368852789166</v>
+        <v>0.9911921458029664</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3.748124945675535</v>
+        <v>0.1326436317656008</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6138</v>
+        <v>5871</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>649.2717677513147</v>
+        <v>651.8740960686548</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>313</v>
+        <v>121.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.63591287410598</v>
+        <v>64.43053422146244</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>30.53038079991035</v>
+        <v>21.67158100638257</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4271767751314706</v>
+        <v>0.6874096068654809</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-7.25121136675785</v>
+        <v>1.263013932495586</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5607</v>
+        <v>5288</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>遠雄港</t>
+          <t>豐祥-KY</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>646.274127638462</v>
+        <v>651.6436885278916</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>52.5</v>
+        <v>190.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.72608459681776</v>
+        <v>80.09878817280384</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.77883867901114</v>
+        <v>24.81852206844126</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.127412763846202</v>
+        <v>2.164368852789166</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1063040497416107</v>
+        <v>3.748124945675535</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5522</v>
+        <v>6138</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>645.2788973444104</v>
+        <v>649.2717677513147</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>66.00681310805911</v>
+        <v>52.63591287410598</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>30.57905666353019</v>
+        <v>30.53038079991035</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.027889734441042</v>
+        <v>0.4271767751314706</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.7663898276494727</v>
+        <v>-7.25121136675785</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4540</v>
+        <v>5607</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>全球傳動</t>
+          <t>遠雄港</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>632.0312418421041</v>
+        <v>646.274127638462</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>61.5</v>
+        <v>52.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>42.57644890434555</v>
+        <v>59.72608459681776</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.50658728501962</v>
+        <v>26.77883867901114</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.203124184210409</v>
+        <v>1.127412763846202</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-1.758929211844332</v>
+        <v>0.1063040497416107</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4590</v>
+        <v>5522</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>富田-創</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>630.0219418760104</v>
+        <v>645.2788973444104</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>57.20854745525005</v>
+        <v>66.00681310805911</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9.114978911194671</v>
+        <v>30.57905666353019</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.502194187601041</v>
+        <v>1.027889734441042</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.4163277367384285</v>
+        <v>0.7663898276494727</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4552</v>
+        <v>4540</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>力達-KY</t>
+          <t>全球傳動</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>615.9183249611641</v>
+        <v>632.0312418421041</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21.3</v>
+        <v>61.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>68.80019328037645</v>
+        <v>42.57644890434555</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.95456620673193</v>
+        <v>23.50658728501962</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5918324961164128</v>
+        <v>0.203124184210409</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1358721978772211</v>
+        <v>-1.758929211844332</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5706</v>
+        <v>4590</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>鳳凰</t>
+          <t>富田-創</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>614.6768671322377</v>
+        <v>630.0219418760104</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>53</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.86055364841405</v>
+        <v>57.20854745525005</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.83196793772564</v>
+        <v>9.114978911194671</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.467686713223772</v>
+        <v>1.502194187601041</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1791063717421707</v>
+        <v>0.4163277367384285</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6134</v>
+        <v>4552</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>萬旭</t>
+          <t>力達-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>609.8065294047511</v>
+        <v>615.9183249611641</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>35.5</v>
+        <v>21.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.87331748090049</v>
+        <v>68.80019328037645</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16.63701937318327</v>
+        <v>28.95456620673193</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.480652940475111</v>
+        <v>0.5918324961164128</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1026859230711998</v>
+        <v>0.1358721978772211</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6147</v>
+        <v>5706</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>鳳凰</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>580.5915877400934</v>
+        <v>614.6768671322377</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>224</v>
+        <v>53</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>48.56673813302986</v>
+        <v>60.86055364841405</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>42.7302447584561</v>
+        <v>20.83196793772564</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5591587740093359</v>
+        <v>1.467686713223772</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-9.968600529177866</v>
+        <v>0.1791063717421707</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4526</v>
+        <v>6134</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>東台</t>
+          <t>萬旭</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>574.2659520940425</v>
+        <v>609.8065294047511</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>38.8</v>
+        <v>35.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.02662036092632</v>
+        <v>56.87331748090049</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.54989817504964</v>
+        <v>16.63701937318327</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4265952094042546</v>
+        <v>1.480652940475111</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.5188683101626155</v>
+        <v>-0.1026859230711998</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6161</v>
+        <v>6147</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>567.6966915577181</v>
+        <v>580.5915877400934</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>53.7</v>
+        <v>224</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.10617725766288</v>
+        <v>48.56673813302986</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>29.48362148949524</v>
+        <v>42.7302447584561</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2696691557718075</v>
+        <v>0.5591587740093359</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.924938631354168</v>
+        <v>-9.968600529177866</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6154</v>
+        <v>4526</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>順發</t>
+          <t>東台</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>564.7504469276257</v>
+        <v>574.2659520940425</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>14</v>
+        <v>38.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>67.22459775592137</v>
+        <v>49.02662036092632</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>33.9232700398535</v>
+        <v>31.54989817504964</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9750446927625688</v>
+        <v>0.4265952094042546</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0511527927926891</v>
+        <v>-0.5188683101626155</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>4771</v>
+        <v>6161</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>望隼</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>562.956548407634</v>
+        <v>567.6966915577181</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>189.5</v>
+        <v>53.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45.58145222897669</v>
+        <v>53.10617725766288</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20.43245456894479</v>
+        <v>29.48362148949524</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2956548407634033</v>
+        <v>0.2696691557718075</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.332154396817808</v>
+        <v>-0.924938631354168</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5533</v>
+        <v>6154</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>皇鼎</t>
+          <t>順發</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>562.4613228904702</v>
+        <v>564.7504469276257</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>14.15</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.12861551507454</v>
+        <v>67.22459775592137</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>23.18474650808605</v>
+        <v>33.9232700398535</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.746132289047019</v>
+        <v>0.9750446927625688</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0338434455570572</v>
+        <v>0.0511527927926891</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, bb_squeeze_breakout, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6163</v>
+        <v>4771</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>望隼</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>549.8353726938251</v>
+        <v>562.956548407634</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>51.3</v>
+        <v>189.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>44.99735080994159</v>
+        <v>45.58145222897669</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16.08645128461654</v>
+        <v>20.43245456894479</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4835372693825023</v>
+        <v>0.2956548407634033</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.038416310848961</v>
+        <v>-1.332154396817808</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4763</v>
+        <v>5533</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>皇鼎</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>546.3376671323173</v>
+        <v>562.4613228904702</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>44.45</v>
+        <v>14.15</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.38804587476507</v>
+        <v>56.12861551507454</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.55906620273338</v>
+        <v>23.18474650808605</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6337667132317224</v>
+        <v>0.746132289047019</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2711607111584255</v>
+        <v>0.0338434455570572</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5876</v>
+        <v>6163</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>540.9320017021437</v>
+        <v>549.8353726938251</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>42.5</v>
+        <v>51.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>65.72164553116424</v>
+        <v>44.99735080994159</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.75880177185082</v>
+        <v>16.08645128461654</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5932001702143697</v>
+        <v>0.4835372693825023</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2438104614392837</v>
+        <v>0.038416310848961</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>4438</v>
+        <v>4763</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>廣越</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>538.3971266269264</v>
+        <v>546.3376671323173</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>61.3</v>
+        <v>44.45</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>55.178104893351</v>
+        <v>55.38804587476507</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>34.32352573717261</v>
+        <v>16.55906620273338</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3397126626926355</v>
+        <v>0.6337667132317224</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0546381674837151</v>
+        <v>0.2711607111584255</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6160</v>
+        <v>5876</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>欣技</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>514.5766219033492</v>
+        <v>540.9320017021437</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>16.6</v>
+        <v>42.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>49.20469353948581</v>
+        <v>65.72164553116424</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.4651235663377</v>
+        <v>24.75880177185082</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4576621903349186</v>
+        <v>0.5932001702143697</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0704764380931923</v>
+        <v>0.2438104614392837</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6150</v>
+        <v>4438</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>撼訊</t>
+          <t>廣越</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>514.3813833823358</v>
+        <v>538.3971266269264</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>64</v>
+        <v>61.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46.54470597572633</v>
+        <v>55.178104893351</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30.47200475009579</v>
+        <v>34.32352573717261</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4381383382335825</v>
+        <v>0.3397126626926355</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.223768221994706</v>
+        <v>0.0546381674837151</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>4576</v>
+        <v>6160</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>大銀微系統</t>
+          <t>欣技</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>513.80673772425</v>
+        <v>514.5766219033492</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>202</v>
+        <v>16.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>39.70785523710782</v>
+        <v>49.20469353948581</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29.51934247063729</v>
+        <v>23.4651235663377</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3806737724249932</v>
+        <v>0.4576621903349186</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-8.893545070782212</v>
+        <v>-0.0704764380931923</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>4551</v>
+        <v>6150</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>智伸科</t>
+          <t>撼訊</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>509.4631667907052</v>
+        <v>514.3813833823358</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.87005955445518</v>
+        <v>46.54470597572633</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.58684024085672</v>
+        <v>30.47200475009579</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.446316679070517</v>
+        <v>0.4381383382335825</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.391252052779506</v>
+        <v>-1.223768221994706</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>4532</v>
+        <v>4576</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>瑞智</t>
+          <t>大銀微系統</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>508.2288948244481</v>
+        <v>513.80673772425</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>24.45</v>
+        <v>202</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.6569626602124</v>
+        <v>39.70785523710782</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.49973080472621</v>
+        <v>29.51934247063729</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8228894824448046</v>
+        <v>0.3806737724249932</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0539705573638513</v>
+        <v>-8.893545070782212</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5284</v>
+        <v>4551</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>jpp-KY</t>
+          <t>智伸科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>503.5638573370229</v>
+        <v>509.4631667907052</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>364</v>
+        <v>152</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>42.26154119614923</v>
+        <v>55.87005955445518</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>33.8196459817527</v>
+        <v>23.58684024085672</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3563857337022847</v>
+        <v>1.446316679070517</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-10.89784437541782</v>
+        <v>-1.391252052779506</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>4764</v>
+        <v>4532</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>雙鍵</t>
+          <t>瑞智</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>501.6565049219275</v>
+        <v>508.2288948244481</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>263</v>
+        <v>24.45</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.49143281139633</v>
+        <v>54.6569626602124</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24.32403480522624</v>
+        <v>21.49973080472621</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6656504921927479</v>
+        <v>0.8228894824448046</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-9.936137197988836</v>
+        <v>0.0539705573638513</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5608</v>
+        <v>5284</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>四維航</t>
+          <t>jpp-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>501.0786991239698</v>
+        <v>503.5638573370229</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15.1</v>
+        <v>364</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.27545012169955</v>
+        <v>42.26154119614923</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.83013829832194</v>
+        <v>33.8196459817527</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.107869912396978</v>
+        <v>0.3563857337022847</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0962238563934984</v>
+        <v>-10.89784437541782</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6151</v>
+        <v>4764</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>晉倫</t>
+          <t>雙鍵</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>494.3010161504799</v>
+        <v>501.6565049219275</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>42.25</v>
+        <v>263</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.47051440175981</v>
+        <v>42.49143281139633</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.42579529398537</v>
+        <v>24.32403480522624</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4301016150479907</v>
+        <v>0.6656504921927479</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.7758281464147181</v>
+        <v>-9.936137197988836</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2700,21 +2700,21 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>4571</v>
+        <v>5608</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>鈞興-KY</t>
+          <t>四維航</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>491.9327501346883</v>
+        <v>501.0786991239698</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>181</v>
+        <v>15.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>40.2176587302068</v>
+        <v>53.27545012169955</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.91477239412865</v>
+        <v>17.83013829832194</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.193275013468833</v>
+        <v>1.107869912396978</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-5.167156155183476</v>
+        <v>0.0962238563934984</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>4766</v>
+        <v>6151</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>晉倫</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>482.2748399532234</v>
+        <v>494.3010161504799</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>369.5</v>
+        <v>42.25</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.90326054770344</v>
+        <v>50.47051440175981</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.69535702202758</v>
+        <v>29.42579529398537</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7274839953223392</v>
+        <v>0.4301016150479907</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.066181100628859</v>
+        <v>-0.7758281464147181</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>4722</v>
+        <v>4571</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>國精化</t>
+          <t>鈞興-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>457.1577539625247</v>
+        <v>491.9327501346883</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>226.5</v>
+        <v>181</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.21244415248516</v>
+        <v>40.2176587302068</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>34.72822445618091</v>
+        <v>27.91477239412865</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.7157753962524703</v>
+        <v>0.193275013468833</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-9.973818307947893</v>
+        <v>-5.167156155183476</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>5283</v>
+        <v>4766</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>禾聯碩</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>423.3832907302466</v>
+        <v>482.2748399532234</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>52.8</v>
+        <v>369.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.89472926324697</v>
+        <v>51.90326054770344</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.60115222852542</v>
+        <v>20.69535702202758</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8383290730246669</v>
+        <v>0.7274839953223392</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0732836356062205</v>
+        <v>-1.066181100628859</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>4572</v>
+        <v>4722</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>駐龍</t>
+          <t>國精化</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>419.98176758656</v>
+        <v>457.1577539625247</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>146.5</v>
+        <v>226.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.6829374225024</v>
+        <v>43.21244415248516</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.90491416473165</v>
+        <v>34.72822445618091</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4981767586559995</v>
+        <v>0.7157753962524703</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0110195295631874</v>
+        <v>-9.973818307947893</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6146</v>
+        <v>5283</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>耕興</t>
+          <t>禾聯碩</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>410.374128286865</v>
+        <v>423.3832907302466</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>196.5</v>
+        <v>52.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>34.42288300657671</v>
+        <v>51.89472926324697</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.94704397734914</v>
+        <v>28.60115222852542</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5374128286864998</v>
+        <v>0.8383290730246669</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-3.264577896901289</v>
+        <v>0.0732836356062205</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>4583</v>
+        <v>4572</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台灣精銳</t>
+          <t>駐龍</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>399.0331525499705</v>
+        <v>419.98176758656</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>618</v>
+        <v>146.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>30.51596390758378</v>
+        <v>52.6829374225024</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.43308385761656</v>
+        <v>15.90491416473165</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4033152549970494</v>
+        <v>0.4981767586559995</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-10.07224136430187</v>
+        <v>-0.0110195295631874</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>4720</v>
+        <v>6146</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>德淵</t>
+          <t>耕興</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>397.5845593113453</v>
+        <v>410.374128286865</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>23.75</v>
+        <v>196.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44.35533474980614</v>
+        <v>34.42288300657671</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.20410049372494</v>
+        <v>23.94704397734914</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2584559311345359</v>
+        <v>0.5374128286864998</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.4561767206110738</v>
+        <v>-3.264577896901289</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>4190</v>
+        <v>4583</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>佐登-KY</t>
+          <t>台灣精銳</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>384.7716815172797</v>
+        <v>399.0331525499705</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>24.9</v>
+        <v>618</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.98360023765276</v>
+        <v>30.51596390758378</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>35.65717014941538</v>
+        <v>23.43308385761656</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4771681517279719</v>
+        <v>0.4033152549970494</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0782318404858611</v>
+        <v>-10.07224136430187</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>4414</v>
+        <v>4720</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>如興</t>
+          <t>德淵</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>383.44496987676</v>
+        <v>397.5845593113453</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>8.43</v>
+        <v>23.75</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>42.76385457042957</v>
+        <v>44.35533474980614</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>27.74456322449394</v>
+        <v>26.20410049372494</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8444969876760019</v>
+        <v>0.2584559311345359</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1336819164384629</v>
+        <v>-0.4561767206110738</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4566</v>
+        <v>4190</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>時碩工業</t>
+          <t>佐登-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>382.6040252124653</v>
+        <v>384.7716815172797</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>63.2</v>
+        <v>24.9</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45.90844489648742</v>
+        <v>48.98360023765276</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14.63513510167739</v>
+        <v>35.65717014941538</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7604025212465264</v>
+        <v>0.4771681517279719</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.571406368507118</v>
+        <v>0.0782318404858611</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>5531</v>
+        <v>4414</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鄉林</t>
+          <t>如興</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>380.8494245271468</v>
+        <v>383.44496987676</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>8.15</v>
+        <v>8.43</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.24769061786547</v>
+        <v>42.76385457042957</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>29.94618955688911</v>
+        <v>27.74456322449394</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.584942452714677</v>
+        <v>0.8444969876760019</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0781016706339439</v>
+        <v>0.1336819164384629</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>5525</v>
+        <v>4566</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>順天</t>
+          <t>時碩工業</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>379.9007307898736</v>
+        <v>382.6040252124653</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>22.3</v>
+        <v>63.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.38608703467234</v>
+        <v>45.90844489648742</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>32.42467569093063</v>
+        <v>14.63513510167739</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4900730789873567</v>
+        <v>0.7604025212465264</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1590350425416684</v>
+        <v>-0.571406368507118</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>5538</v>
+        <v>5531</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>東明-KY</t>
+          <t>鄉林</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>374.2403813201082</v>
+        <v>380.8494245271468</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>32.45</v>
+        <v>8.15</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.37380752633383</v>
+        <v>52.24769061786547</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>32.84678507059154</v>
+        <v>29.94618955688911</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4240381320108234</v>
+        <v>0.584942452714677</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.50265201916005</v>
+        <v>0.0781016706339439</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4930</v>
+        <v>5525</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>燦星網</t>
+          <t>順天</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>359.7198418646074</v>
+        <v>379.9007307898736</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>17.35</v>
+        <v>22.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.7333892054443</v>
+        <v>49.38608703467234</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>34.25901702495012</v>
+        <v>32.42467569093063</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4719841864607431</v>
+        <v>0.4900730789873567</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0277719202176923</v>
+        <v>0.1590350425416684</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4562</v>
+        <v>5538</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>穎漢</t>
+          <t>東明-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>356.6730637846136</v>
+        <v>374.2403813201082</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>35.8</v>
+        <v>32.45</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>41.90967229766305</v>
+        <v>43.37380752633383</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.56056004664616</v>
+        <v>32.84678507059154</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.1673063784613569</v>
+        <v>0.4240381320108234</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.9582201256015994</v>
+        <v>-0.50265201916005</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>5907</v>
+        <v>4930</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>大洋-KY</t>
+          <t>燦星網</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>348.9084043967841</v>
+        <v>359.7198418646074</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>5.05</v>
+        <v>17.35</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>44.43552465861959</v>
+        <v>43.7333892054443</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>24.46292482884273</v>
+        <v>34.25901702495012</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.390840439678415</v>
+        <v>0.4719841864607431</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.019279633521072</v>
+        <v>0.0277719202176923</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4439</v>
+        <v>4562</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>冠星-KY</t>
+          <t>穎漢</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>337.3136490250697</v>
+        <v>356.6730637846136</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>35.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>42.65481014856325</v>
+        <v>41.90967229766305</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46.41719972313586</v>
+        <v>23.56056004664616</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.231364902506964</v>
+        <v>0.1673063784613569</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1616945748844021</v>
+        <v>-0.9582201256015994</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6143</v>
+        <v>5907</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>振曜</t>
+          <t>大洋-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>334.2136402283606</v>
+        <v>348.9084043967841</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>90.7</v>
+        <v>5.05</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.23101420571027</v>
+        <v>44.43552465861959</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>26.2865273900439</v>
+        <v>24.46292482884273</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4213640228360623</v>
+        <v>0.390840439678415</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.173885316988266</v>
+        <v>0.019279633521072</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4426</v>
+        <v>4439</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>利勤</t>
+          <t>冠星-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>323.9195357366331</v>
+        <v>337.3136490250697</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>8.01</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.68984921352049</v>
+        <v>42.65481014856325</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.86685742146232</v>
+        <v>46.41719972313586</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3919535736633125</v>
+        <v>1.231364902506964</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0176346679571385</v>
+        <v>-0.1616945748844021</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>4737</v>
+        <v>6143</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>華廣</t>
+          <t>振曜</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>309.8989310899742</v>
+        <v>334.2136402283606</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>54.9</v>
+        <v>90.7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>41.8516616153643</v>
+        <v>39.23101420571027</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>25.60136555828307</v>
+        <v>26.2865273900439</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4898931089974225</v>
+        <v>0.4213640228360623</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0302076607319334</v>
+        <v>-1.173885316988266</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>4581</v>
+        <v>4426</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>光隆精密-KY</t>
+          <t>利勤</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>292.4156195413309</v>
+        <v>323.9195357366331</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>49.65</v>
+        <v>8.01</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>51.65028856950888</v>
+        <v>47.68984921352049</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>25.11037560195356</v>
+        <v>21.86685742146232</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.241561954133093</v>
+        <v>0.3919535736633125</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.5143923587615937</v>
+        <v>0.0176346679571385</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>4755</v>
+        <v>4737</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>三福化</t>
+          <t>華廣</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>291.6719102960272</v>
+        <v>309.8989310899742</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>140</v>
+        <v>54.9</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.61759100969651</v>
+        <v>41.8516616153643</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.36591962028105</v>
+        <v>25.60136555828307</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6671910296027268</v>
+        <v>0.4898931089974225</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.387614401314258</v>
+        <v>0.0302076607319334</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>5521</v>
+        <v>4581</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>工信</t>
+          <t>光隆精密-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>287.2582142974125</v>
+        <v>292.4156195413309</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10.55</v>
+        <v>49.65</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.05597778740637</v>
+        <v>51.65028856950888</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27.34548898249981</v>
+        <v>25.11037560195356</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.225821429741244</v>
+        <v>1.241561954133093</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1236454581342041</v>
+        <v>0.5143923587615937</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>4560</v>
+        <v>4755</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>強信-KY</t>
+          <t>三福化</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>285.0919122674075</v>
+        <v>291.6719102960272</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>32.55</v>
+        <v>140</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46.26830378037008</v>
+        <v>45.61759100969651</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.25026302152018</v>
+        <v>18.36591962028105</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.009191226740745</v>
+        <v>0.6671910296027268</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0544025902947936</v>
+        <v>-1.387614401314258</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>4195</v>
+        <v>5521</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>基米-創</t>
+          <t>工信</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>260.673408466547</v>
+        <v>287.2582142974125</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>16.3</v>
+        <v>10.55</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>26.88019506963234</v>
+        <v>47.05597778740637</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45.2260666595232</v>
+        <v>27.34548898249981</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5673408466546973</v>
+        <v>1.225821429741244</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2831333050658653</v>
+        <v>0.1236454581342041</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>5906</v>
+        <v>4560</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台南-KY</t>
+          <t>強信-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>255</v>
+        <v>285.0919122674075</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0</v>
+        <v>32.55</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.04470615296958</v>
+        <v>46.26830378037008</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7.91364784163176</v>
+        <v>18.25026302152018</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0</v>
+        <v>1.009191226740745</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-1.849094838025186</v>
+        <v>0.0544025902947936</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4131,21 +4131,21 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>4564</v>
+        <v>4195</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>元翎</t>
+          <t>基米-創</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>250.6963381814243</v>
+        <v>260.673408466547</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15.45</v>
+        <v>16.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>37.83417426734455</v>
+        <v>26.88019506963234</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>38.6958056533116</v>
+        <v>45.2260666595232</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5696338181424268</v>
+        <v>0.5673408466546973</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.06597526466791299</v>
+        <v>0.2831333050658653</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>4736</v>
+        <v>5906</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>泰博</t>
+          <t>台南-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>221.8642497192834</v>
+        <v>255</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>124.5</v>
+        <v>0</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.61204993260861</v>
+        <v>46.04470615296958</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>12.50085462856218</v>
+        <v>7.91364784163176</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6864249719283386</v>
+        <v>0</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1974116866264246</v>
+        <v>-1.849094838025186</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>4569</v>
+        <v>4564</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>元翎</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>197.8100968716587</v>
+        <v>250.6963381814243</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>167.5</v>
+        <v>15.45</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.12657809803279</v>
+        <v>37.83417426734455</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.74161803794673</v>
+        <v>38.6958056533116</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7810096871658698</v>
+        <v>0.5696338181424268</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.670990161110644</v>
+        <v>0.06597526466791299</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>4746</v>
+        <v>4736</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>泰博</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>175.2351537526606</v>
+        <v>221.8642497192833</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>51.5</v>
+        <v>124.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.64154034557406</v>
+        <v>50.61204993260861</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9.486846813901066</v>
+        <v>12.50085462856218</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5235153752660638</v>
+        <v>0.6864249719283386</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0243230316248074</v>
+        <v>0.1974116866264246</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>5007</v>
+        <v>4569</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>三星</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>172.7274487114792</v>
+        <v>197.8100968716587</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>56.5</v>
+        <v>167.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.30253361046012</v>
+        <v>46.12657809803279</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.28948318410757</v>
+        <v>16.74161803794673</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2727448711479232</v>
+        <v>0.7810096871658698</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.1012909274172315</v>
+        <v>-1.670990161110644</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6158</v>
+        <v>4746</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>禾昌</t>
+          <t>台耀</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>166.9668411193295</v>
+        <v>175.2351537526606</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>17.45</v>
+        <v>51.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>34.14393374638051</v>
+        <v>44.64154034557406</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.58761649835379</v>
+        <v>9.486846813901066</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.696684111932948</v>
+        <v>0.5235153752660638</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0188410825470713</v>
+        <v>-0.0243230316248074</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>4557</v>
+        <v>5007</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>永新-KY</t>
+          <t>三星</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>166.4967820064115</v>
+        <v>172.7274487114792</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>46.75</v>
+        <v>56.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.43621242024396</v>
+        <v>45.30253361046012</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>27.22166125974199</v>
+        <v>19.28948318410757</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6496782006411473</v>
+        <v>0.2727448711479232</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.554729176980004</v>
+        <v>-0.1012909274172315</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>5546</v>
+        <v>6158</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>永固-KY</t>
+          <t>禾昌</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>148.8082868321468</v>
+        <v>166.9668411193295</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>16.75</v>
+        <v>17.45</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.81536816498284</v>
+        <v>34.14393374638051</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>23.09248744234548</v>
+        <v>13.58761649835379</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3808286832146751</v>
+        <v>1.696684111932948</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0242443830419427</v>
+        <v>-0.0188410825470713</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>4441</v>
+        <v>4557</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>振大環球</t>
+          <t>永新-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>143.8922409045892</v>
+        <v>166.4967820064115</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>193.5</v>
+        <v>46.75</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.14477763333788</v>
+        <v>48.43621242024396</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>17.97233820215637</v>
+        <v>27.22166125974199</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.389224090458924</v>
+        <v>0.6496782006411473</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-2.115490011180428</v>
+        <v>0.554729176980004</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>4440</v>
+        <v>5546</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>宜新實業</t>
+          <t>永固-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>124.4567220321029</v>
+        <v>148.8082868321468</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>17.15</v>
+        <v>16.75</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.99893325828462</v>
+        <v>50.81536816498284</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.63463066133024</v>
+        <v>23.09248744234548</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4456722032102861</v>
+        <v>0.3808286832146751</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,62 +4651,168 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1217247489635101</v>
+        <v>0.0242443830419427</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
+        <v>4441</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>振大環球</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>143.8922409045892</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>42.14477763333788</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>17.97233820215637</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.389224090458924</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-2.115490011180428</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>4440</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>宜新實業</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>124.4567220321029</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>37.99893325828462</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>16.63463066133024</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.4456722032102861</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-0.1217247489635101</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
         <v>4770</v>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>上品</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D80" s="2" t="n">
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
         <v>123.9487978910787</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E82" s="2" t="n">
         <v>213.5</v>
       </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
         <v>35.14166795768833</v>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="I82" s="2" t="n">
         <v>18.97149326314445</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J82" s="2" t="n">
         <v>0.3948797891078702</v>
       </c>
-      <c r="K80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N80" s="2" t="n">
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
         <v>-4.525715643062574</v>
       </c>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>

--- a/output/full_scan/batch_seq5_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq5_2026-06-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4958</v>
+        <v>5536</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1222.124772633198</v>
+        <v>1206.518778060672</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>552</v>
+        <v>1180</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>62.8249259025986</v>
+        <v>65.5652511258279</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>32.22530634135668</v>
+        <v>30.96359253525273</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.712477263319851</v>
+        <v>0.651877806067151</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-3.803204346301186</v>
+        <v>5.042497790292259</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5536</v>
+        <v>4958</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1191.518778060672</v>
+        <v>1197.124772633198</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1180</v>
+        <v>552</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,29 +605,29 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>65.56525112738298</v>
+        <v>62.82492590205248</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>30.96359252454072</v>
+        <v>32.22530631690136</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.651877806067151</v>
+        <v>1.712477263319851</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5.04249779076936</v>
+        <v>-3.803204346511045</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1032.66951940095</v>
+        <v>1047.66951940095</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>66.2</v>
@@ -661,7 +661,7 @@
         <v>74.96612752552497</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>35.57997207527055</v>
+        <v>35.57997207356249</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0.7669519400950385</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.361487171017293</v>
+        <v>1.361487170988673</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>995.5037431591938</v>
+        <v>1010.503743159194</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>24.95</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.08226596546063</v>
+        <v>58.08226585246314</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.61679793950268</v>
+        <v>20.61679804207909</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.050374315919388</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2504878029721644</v>
+        <v>0.2504878031534194</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>989.813535800476</v>
+        <v>1004.813535800476</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>69.40000000000001</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.09605927597422</v>
+        <v>55.09605927852982</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14.1277473791551</v>
+        <v>14.12774742578618</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3.981353580047599</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.3359777673124215</v>
+        <v>0.3359777672761554</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4904</v>
+        <v>5450</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>寶聯通</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>980.5445958050822</v>
+        <v>961.0467760935004</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>109</v>
+        <v>15.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>78.12292250142181</v>
+        <v>74.31535967786571</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33.37014651659936</v>
+        <v>30.41518323537224</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.054459580508211</v>
+        <v>3.104677609350048</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.273915732665974</v>
+        <v>0.2638105991181027</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6153</v>
+        <v>5483</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>嘉聯益</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>959.423367749197</v>
+        <v>956.866507829208</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>22.25</v>
+        <v>159</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>68.86527159019502</v>
+        <v>54.94971952142578</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19.84225679458477</v>
+        <v>22.93281192040306</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.4423367749197</v>
+        <v>1.186650782920809</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3160910305170158</v>
+        <v>-1.990660915622472</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, invest_trust_buy_2d, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5483</v>
+        <v>6113</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>亞矽</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>956.866507829208</v>
+        <v>956.1360204508726</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>159</v>
+        <v>27.25</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>54.94971949039071</v>
+        <v>59.40918683545784</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.93281182597446</v>
+        <v>28.24822204501992</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.186650782920809</v>
+        <v>1.613602045087264</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-1.990660915298125</v>
+        <v>-0.1227078309524257</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, invest_trust_buy_2d, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6113</v>
+        <v>4904</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>亞矽</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>956.1360204508726</v>
+        <v>955.5445958050822</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>27.25</v>
+        <v>109</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>59.40918696475736</v>
+        <v>78.12292245908347</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.24822228346461</v>
+        <v>33.37014660274721</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.613602045087264</v>
+        <v>1.054459580508211</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1227078311432208</v>
+        <v>1.273915732646895</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5450</v>
+        <v>5489</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>寶聯通</t>
+          <t>彩富</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>946.0467760935004</v>
+        <v>951.7591326876566</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15.3</v>
+        <v>40.65</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>74.31535957810459</v>
+        <v>58.56150934084034</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.4151832045692</v>
+        <v>31.37279062021691</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.104677609350048</v>
+        <v>0.6759132687656579</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.2638105991753409</v>
+        <v>0.1232170417687093</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5489</v>
+        <v>6153</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>彩富</t>
+          <t>嘉聯益</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>936.7591326876566</v>
+        <v>934.423367749197</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>40.65</v>
+        <v>22.25</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.5615099076789</v>
+        <v>68.86527160057717</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.37279052737924</v>
+        <v>19.84225692628262</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6759132687656579</v>
+        <v>2.4423367749197</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.123217040833819</v>
+        <v>0.3160910304693161</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5471</v>
+        <v>5228</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>松翰</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>918.1485119850972</v>
+        <v>915.948638221754</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>54.2</v>
+        <v>69.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>59.52424019339415</v>
+        <v>68.85182215932876</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.76116677525499</v>
+        <v>49.1133555704927</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.814851198509728</v>
+        <v>1.594863822175408</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.441377788218342</v>
+        <v>0.0450358428298436</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4952</v>
+        <v>5457</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>宣德</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>909.1313160042027</v>
+        <v>913.4896915673075</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>53.8</v>
+        <v>35.55</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.78786777008337</v>
+        <v>62.69388833735386</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23.8048330876266</v>
+        <v>18.77976256485323</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.913131600420273</v>
+        <v>1.848969156730766</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.2677798551035965</v>
+        <v>0.625288888576486</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5228</v>
+        <v>5328</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>華容</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>900.948638221754</v>
+        <v>891.7789011167667</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>69.3</v>
+        <v>42.35</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>68.85182280673132</v>
+        <v>66.06797582025118</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>49.11335624673118</v>
+        <v>33.67682053260449</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.594863822175408</v>
+        <v>1.177890111676673</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0450358399774684</v>
+        <v>0.3178852106057817</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5457</v>
+        <v>5468</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>宣德</t>
+          <t>凱鈺</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>898.4896915673077</v>
+        <v>874.1511807687895</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>35.55</v>
+        <v>21.75</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.69388832287841</v>
+        <v>76.84986203287342</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18.77976252803274</v>
+        <v>14.94360561356622</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.848969156730766</v>
+        <v>2.415118076878948</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.6252888887005044</v>
+        <v>0.3458689310136037</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6139</v>
+        <v>4952</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>凌通</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>885.2195102480873</v>
+        <v>869.1313160042027</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>805</v>
+        <v>53.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.96279197945687</v>
+        <v>57.78786781721301</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.98279043496008</v>
+        <v>23.80483315786083</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.021951024808735</v>
+        <v>2.913131600420273</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-6.455213113112443</v>
+        <v>-0.2677798554661073</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5328</v>
+        <v>5289</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>華容</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>876.7789011167667</v>
+        <v>862.3990483143142</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>42.35</v>
+        <v>1805</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>66.06797581145457</v>
+        <v>54.7084066933186</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.67682041980587</v>
+        <v>29.3549118944077</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.177890111676673</v>
+        <v>0.7399048314314181</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.3178852106725562</v>
+        <v>-25.9117838441374</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5434</v>
+        <v>5471</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>松翰</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>862.6075325942804</v>
+        <v>858.1485119850972</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>466</v>
+        <v>54.2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.95139095083398</v>
+        <v>59.52424022480326</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.0944342106283</v>
+        <v>29.76116687061658</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.260753259428041</v>
+        <v>1.814851198509728</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-2.066519706626838</v>
+        <v>-0.4413777884186758</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5289</v>
+        <v>6139</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>862.3990483143142</v>
+        <v>845.2195102480873</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1805</v>
+        <v>805</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.7084066933186</v>
+        <v>57.96279198325738</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.35491190395361</v>
+        <v>22.98279045827245</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7399048314314181</v>
+        <v>1.021951024808735</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-25.9117838430881</v>
+        <v>-6.455213112921498</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5468</v>
+        <v>5425</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>凱鈺</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>859.1511807687895</v>
+        <v>831.8284250376296</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21.75</v>
+        <v>101</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>76.8498619301775</v>
+        <v>58.95962958734327</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.94360555776429</v>
+        <v>35.11866555903156</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.415118076878948</v>
+        <v>0.6828425037629546</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.345868931147158</v>
+        <v>-2.087345032056202</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4934</v>
+        <v>6155</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>834.3423468780192</v>
+        <v>817.3061265891887</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>17.7</v>
+        <v>82</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.45788255627393</v>
+        <v>68.11789014646821</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13.13170869623832</v>
+        <v>44.61785823245832</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3.434234687801918</v>
+        <v>1.730612658918865</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0039027119664011</v>
+        <v>1.220416227817563</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5425</v>
+        <v>5434</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>831.8284250376296</v>
+        <v>812.6075325942804</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>101</v>
+        <v>466</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>58.95962958861768</v>
+        <v>58.95139100896203</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>35.11866548298713</v>
+        <v>24.09443458910519</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6828425037629546</v>
+        <v>1.260753259428041</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-2.087345031903574</v>
+        <v>-2.06651970872552</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4915</v>
+        <v>5356</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>協益</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>831.202039177061</v>
+        <v>803.8629639248924</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>76.5</v>
+        <v>28</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.07368215466612</v>
+        <v>64.19802861990655</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14.49231825982016</v>
+        <v>28.05541241520336</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.120203917706104</v>
+        <v>1.386296392489236</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1681542557706391</v>
+        <v>0.08642927717934359</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6155</v>
+        <v>5309</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>827.3061265891887</v>
+        <v>798.9348050985494</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>82</v>
+        <v>69.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>68.11789013940532</v>
+        <v>50.29396816834935</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>44.61785815555402</v>
+        <v>24.14339590925458</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.730612658918865</v>
+        <v>0.3934805098549379</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.220416227884332</v>
+        <v>-0.9304580354969624</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5285</v>
+        <v>4915</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>界霖</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>823.7935280487106</v>
+        <v>791.202039177061</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>89.7</v>
+        <v>76.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>62.49669276315545</v>
+        <v>57.07368217005797</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>50.06158881480827</v>
+        <v>14.49231831247624</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3793528048710668</v>
+        <v>1.120203917706104</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.337653036930453</v>
+        <v>0.1681542556180078</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5309</v>
+        <v>6121</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>798.9348050985494</v>
+        <v>789.4343663183148</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>69.7</v>
+        <v>411.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.29396813429244</v>
+        <v>60.59155763857528</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>24.14339573610042</v>
+        <v>30.82263636976898</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3934805098549379</v>
+        <v>0.9434366318314784</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.9304580351726216</v>
+        <v>0.2307540015520661</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5356</v>
+        <v>5347</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>協益</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>788.8629639248924</v>
+        <v>787.662718047303</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>28</v>
+        <v>169.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>64.19802862712594</v>
+        <v>55.58399210732704</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>28.05541241520336</v>
+        <v>15.40188611791958</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.386296392489236</v>
+        <v>0.7662718047303009</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0864292771602632</v>
+        <v>-1.417211988100854</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5347</v>
+        <v>4934</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>787.662718047303</v>
+        <v>784.3423468780192</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>169.5</v>
+        <v>17.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.58399210270593</v>
+        <v>55.45788268499557</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15.40188611807175</v>
+        <v>13.13170889452032</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7662718047303009</v>
+        <v>3.434234687801918</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.417211987833727</v>
+        <v>-0.0039027120617996</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6121</v>
+        <v>6126</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>信音</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>774.4343663183148</v>
+        <v>773.0592857351388</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>411.5</v>
+        <v>40.25</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>60.59155761205157</v>
+        <v>57.9126038835308</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.82263627692597</v>
+        <v>30.66645393020256</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.9434366318314784</v>
+        <v>1.805928573513877</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2307540031738089</v>
+        <v>0.1273133437844666</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5464</v>
+        <v>5285</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>霖宏</t>
+          <t>界霖</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>755.7912698571602</v>
+        <v>763.7935280487106</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>71.8</v>
+        <v>89.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.54486385339897</v>
+        <v>62.49669277397012</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>48.63359909214425</v>
+        <v>50.06158880894652</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.079126985716019</v>
+        <v>0.3793528048710668</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.677186311144988</v>
+        <v>-1.337653037025856</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5351</v>
+        <v>5464</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>霖宏</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>749.1659987243305</v>
+        <v>755.7912698571602</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>88.7</v>
+        <v>71.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.55283520796241</v>
+        <v>59.54486384778584</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19.0652611894372</v>
+        <v>48.63359920571053</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9165998724330467</v>
+        <v>1.079126985716019</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.4302076630589675</v>
+        <v>-1.677186311173608</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5488</v>
+        <v>5351</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>松普</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>748.3539624498939</v>
+        <v>749.1659987243305</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>12.15</v>
+        <v>88.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.49481493679817</v>
+        <v>57.55283523159785</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>33.38371554790734</v>
+        <v>19.0652613589299</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3353962449893842</v>
+        <v>0.9165998724330467</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1392713667958188</v>
+        <v>-0.4302076632974616</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6115</v>
+        <v>5488</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>鎰勝</t>
+          <t>松普</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>737.662124787401</v>
+        <v>748.3539624498939</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>48.55</v>
+        <v>12.15</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.96237098514083</v>
+        <v>52.49481489682626</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15.86516582424448</v>
+        <v>33.38371554645537</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7662124787401066</v>
+        <v>0.3353962449893842</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0707970119147928</v>
+        <v>-0.1392713668416093</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>4760</v>
+        <v>5381</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>光譜</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>736.3621578176674</v>
+        <v>744.1009862788502</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>376.5</v>
+        <v>28.05</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>54.38704821151308</v>
+        <v>50.18977893841673</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>29.55569889737388</v>
+        <v>36.44363519575623</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6362157817667358</v>
+        <v>1.910098627885024</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-8.710024905377196</v>
+        <v>0.2255984729058768</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5302</v>
+        <v>4760</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>太欣</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>732.5479075496656</v>
+        <v>736.3621578176674</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11.3</v>
+        <v>376.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.38309598644782</v>
+        <v>54.38704821342394</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18.44735972003102</v>
+        <v>29.55569893321236</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.75479075496656</v>
+        <v>0.6362157817667358</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0720146648069681</v>
+        <v>-8.710024905873311</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5381</v>
+        <v>5302</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>光譜</t>
+          <t>太欣</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>729.1009862788502</v>
+        <v>732.5479075496656</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>28.05</v>
+        <v>11.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.18977887385386</v>
+        <v>55.38309599168608</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>36.4436350079916</v>
+        <v>18.44735973141305</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.910098627885024</v>
+        <v>1.75479075496656</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.2255984731026767</v>
+        <v>0.0720146647630862</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5274</v>
+        <v>4931</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>729.0383151283966</v>
+        <v>729.693637936532</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>18445</v>
+        <v>236</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.89801414984439</v>
+        <v>55.33588764816768</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.82605567774115</v>
+        <v>38.29793597935626</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9038315128396602</v>
+        <v>0.4693637936532045</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-128.5515117396915</v>
+        <v>-1.34662506141505</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>4729</v>
+        <v>5274</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>722.4635152368427</v>
+        <v>729.0383151283966</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>22.1</v>
+        <v>18445</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45.22854393846332</v>
+        <v>57.89801415676981</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>36.63258273713046</v>
+        <v>24.82605577534577</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2463515236842643</v>
+        <v>0.9038315128396602</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.5607052343796375</v>
+        <v>-128.5515117549552</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5490</v>
+        <v>4729</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>同亨</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>718.7701154710114</v>
+        <v>722.4635152368427</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>28.8</v>
+        <v>22.1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.59373798209493</v>
+        <v>45.22854399441817</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27.20576550150855</v>
+        <v>36.63258294323934</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3770115471011395</v>
+        <v>0.2463515236842643</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1520430589188626</v>
+        <v>-0.5607052345895119</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5474</v>
+        <v>5493</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聰泰</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>717.5727494625341</v>
+        <v>722.4408477737055</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>175</v>
+        <v>93.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.08225075746579</v>
+        <v>52.49672346186151</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>30.11562582288233</v>
+        <v>27.18676044282892</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7572749462534148</v>
+        <v>0.744084777370552</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.150630536742543</v>
+        <v>0.061265506874399</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>4931</v>
+        <v>5490</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>同亨</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>714.693637936532</v>
+        <v>718.7701154710114</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>236</v>
+        <v>28.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.33588762197909</v>
+        <v>51.59373818345921</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>38.29793582573085</v>
+        <v>27.20576552097501</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4693637936532045</v>
+        <v>0.3770115471011395</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.346625060480171</v>
+        <v>-0.1520430590333366</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>4919</v>
+        <v>5474</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>聰泰</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>711.2795935293385</v>
+        <v>717.5727494625341</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>175.5</v>
+        <v>175</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>50.30053232986833</v>
+        <v>54.08225085479537</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22.29935249299201</v>
+        <v>30.11562614181517</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.127959352933855</v>
+        <v>0.7572749462534148</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-5.399382827159622</v>
+        <v>-1.15063053826889</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2753,21 +2753,21 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>5493</v>
+        <v>5355</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>佳總</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>707.4408477737055</v>
+        <v>711.6404799227417</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>93.7</v>
+        <v>6.87</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.4967234512177</v>
+        <v>55.81946715835536</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>27.18676026509821</v>
+        <v>15.6669974985708</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.744084777370552</v>
+        <v>0.6640479922741768</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0612655073132379</v>
+        <v>0.0387905283685345</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>4916</v>
+        <v>4919</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>事欣科</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>705.187011032043</v>
+        <v>706.2795935293385</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>107.5</v>
+        <v>175.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.91607495892195</v>
+        <v>50.30053233960906</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45.58280420855623</v>
+        <v>22.29935264286105</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.018701103204296</v>
+        <v>1.127959352933855</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.41066751089863</v>
+        <v>-5.399382827693866</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>5355</v>
+        <v>6116</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>佳總</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>696.6404799227417</v>
+        <v>701.8311289590233</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>6.87</v>
+        <v>15.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.81946709261142</v>
+        <v>54.32649778750781</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.66699746977556</v>
+        <v>40.36346786757292</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6640479922741768</v>
+        <v>0.1831128959023278</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0387905284238652</v>
+        <v>-0.485555694386218</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>4938</v>
+        <v>6115</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>鎰勝</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>688.4174831533853</v>
+        <v>697.662124787401</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>48.55</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>60.42264973711751</v>
+        <v>56.96237100283038</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>30.73501909761734</v>
+        <v>15.86516601205626</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8417483153385362</v>
+        <v>0.7662124787401066</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,11 +2955,11 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3737829552455629</v>
+        <v>0.07079701183847111</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.79553691405904</v>
+        <v>52.79553699841755</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.95387491478208</v>
+        <v>25.95387517524</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.3354241962817954</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2354403698445376</v>
+        <v>-0.2354403701116504</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6133</v>
+        <v>5203</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>金橋</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>672.6041186121496</v>
+        <v>681.0447306745565</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>23.8</v>
+        <v>70</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.29112390998996</v>
+        <v>59.71978847963106</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.68520540011991</v>
+        <v>20.4395473734502</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7604118612149574</v>
+        <v>0.6044730674556463</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.059239052112864</v>
+        <v>0.0798087607743176</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>5203</v>
+        <v>4916</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>事欣科</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>661.0447306745565</v>
+        <v>680.187011032043</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>70</v>
+        <v>107.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>59.71978833193072</v>
+        <v>56.91607497371981</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>20.43954736519398</v>
+        <v>45.58280426254098</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6044730674556463</v>
+        <v>1.018701103204296</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0798087615374756</v>
+        <v>-1.410667511222984</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>5227</v>
+        <v>4906</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>立凱-KY</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>659.3414499676295</v>
+        <v>679.5598965245958</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>30.9</v>
+        <v>44.2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>73.04272485968502</v>
+        <v>51.67569361932198</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>21.94950110107466</v>
+        <v>30.3214263120348</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9341449967629544</v>
+        <v>0.4559896524595848</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.4250492659241902</v>
+        <v>-0.8718986885982858</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>4924</v>
+        <v>5227</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>欣厚-KY</t>
+          <t>立凱-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>657.0494547774396</v>
+        <v>674.3414499676295</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>12.15</v>
+        <v>30.9</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>55.11333393346421</v>
+        <v>73.04272492645647</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>27.06527195072394</v>
+        <v>21.94950113265353</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2049454777439524</v>
+        <v>0.9341449967629544</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,11 +3220,11 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.08127263863197789</v>
+        <v>0.4250492657524762</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>656.7142531238466</v>
+        <v>671.7142531238466</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>20.8</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>58.44764462987095</v>
+        <v>58.44764461921572</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>25.98586257902477</v>
+        <v>25.9858625377009</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.6714253123846583</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1513670856623622</v>
+        <v>0.1513670855669664</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>654.8455651482611</v>
+        <v>669.8455651482611</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>32.25</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>62.26539202579593</v>
+        <v>62.26539213708111</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>61.60837658530764</v>
+        <v>61.60837715454496</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.4845565148261154</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.2236465331371229</v>
+        <v>0.2236465328223131</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>4961</v>
+        <v>4938</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>天鈺</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>654.7059984090013</v>
+        <v>663.4174831533853</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>166</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.91044996455997</v>
+        <v>60.42264969640613</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.65258597092062</v>
+        <v>30.73501906289848</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4705998409001248</v>
+        <v>0.8417483153385362</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,48 +3379,48 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-1.507495900098365</v>
+        <v>0.373782955169248</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>5484</v>
+        <v>4987</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>科誠</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>653.3202375359508</v>
+        <v>662.5086491134235</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>49.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.68686893278248</v>
+        <v>55.06266396898889</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>44.72601942149131</v>
+        <v>23.90739804314249</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3320237535950755</v>
+        <v>0.750864911342356</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.4902879925276844</v>
+        <v>-0.0408812918032386</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4943</v>
+        <v>4924</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>康控-KY</t>
+          <t>欣厚-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>651.7518777387002</v>
+        <v>657.0494547774396</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>9.06</v>
+        <v>12.15</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>47.17512255682482</v>
+        <v>55.11333395192634</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.99793295014436</v>
+        <v>27.06527195567271</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.175187773870018</v>
+        <v>0.2049454777439524</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0564661385344983</v>
+        <v>-0.081272638670137</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4906</v>
+        <v>6123</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>上奇</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>649.5598965245958</v>
+        <v>645.0732517131243</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>44.2</v>
+        <v>46.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.67569361089854</v>
+        <v>58.72084675113165</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>30.32142624246737</v>
+        <v>22.42903906828399</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4559896524595848</v>
+        <v>1.007325171312426</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,51 +3538,51 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.8718986885315103</v>
+        <v>0.1051305250324182</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4987</v>
+        <v>4923</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>科誠</t>
+          <t>力士</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>647.5086491134235</v>
+        <v>643.8480297626918</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>55.06266248350222</v>
+        <v>61.18507038072602</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.90739703685718</v>
+        <v>17.55988468601206</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.750864911342356</v>
+        <v>0.8848029762691836</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0408812903913472</v>
+        <v>-0.1723720922033806</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>5292</v>
+        <v>4961</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>天鈺</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>645.7453004942604</v>
+        <v>634.7059984090013</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.93416689643677</v>
+        <v>48.91045005969329</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.27714156773574</v>
+        <v>21.65258599598889</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.074530049426034</v>
+        <v>0.4705998409001248</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.433967037473384</v>
+        <v>-1.507495901720126</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6123</v>
+        <v>5299</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>上奇</t>
+          <t>杰力</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>645.0732517131243</v>
+        <v>632.8413276341121</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>46.1</v>
+        <v>105.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>58.72084645363059</v>
+        <v>52.07694874367709</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>22.4290389962986</v>
+        <v>40.19058740949689</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.007325171312426</v>
+        <v>0.2841327634112118</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1051305254903149</v>
+        <v>-2.245958961314794</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>5299</v>
+        <v>6133</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>杰力</t>
+          <t>金橋</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>632.8413276341121</v>
+        <v>632.6041186121496</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>105.5</v>
+        <v>23.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.07694869974833</v>
+        <v>54.29112398409503</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>40.19058724838437</v>
+        <v>13.685205509787</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2841327634112118</v>
+        <v>0.7604118612149574</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.245958960837816</v>
+        <v>-0.0592390522464195</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>4923</v>
+        <v>5278</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>力士</t>
+          <t>尚凡</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>628.8480297626918</v>
+        <v>631.9695644153996</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>47.5</v>
+        <v>24.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>61.18507039894923</v>
+        <v>54.86535451119106</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.55988466119567</v>
+        <v>12.94227397481718</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8848029762691836</v>
+        <v>0.6969564415399615</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1723720922606206</v>
+        <v>0.1471835715779106</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>5243</v>
+        <v>4943</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>康控-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>618.6411117933949</v>
+        <v>626.7518777387002</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>111</v>
+        <v>9.06</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,49 +3838,49 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.33467222214117</v>
+        <v>47.1751224944565</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.37395380144481</v>
+        <v>15.99793295014436</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3641111793394835</v>
+        <v>2.175187773870018</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-2.043881150661328</v>
+        <v>0.0564661385344983</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>5278</v>
+        <v>5243</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>尚凡</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>616.9695644153996</v>
+        <v>618.6411117933949</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>24.3</v>
+        <v>111</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.86535457842572</v>
+        <v>47.33467223152136</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.94227387216776</v>
+        <v>19.37395399365654</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6969564415399615</v>
+        <v>0.3641111793394835</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1471835717019308</v>
+        <v>-2.04388115090936</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>4976</v>
+        <v>5484</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>600.6035765844556</v>
+        <v>613.3202375359508</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>32.55</v>
+        <v>49.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.81814557333741</v>
+        <v>52.68686898578913</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>33.84038171178083</v>
+        <v>44.72601965757276</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5603576584455551</v>
+        <v>0.3320237535950755</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0491744936991338</v>
+        <v>-0.490287992966512</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>4974</v>
+        <v>4976</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>亞泰</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>596.2230528468705</v>
+        <v>600.6035765844556</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>76</v>
+        <v>32.55</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.36083306202077</v>
+        <v>51.81814557601687</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.82188688432513</v>
+        <v>33.84038182094574</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6223052846870452</v>
+        <v>0.5603576584455551</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.3464260571007435</v>
+        <v>-0.0491744938136033</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>5236</v>
+        <v>4974</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>凌陽創新</t>
+          <t>亞泰</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>573.9934662928781</v>
+        <v>596.2230528468705</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>159</v>
+        <v>76</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.50466205985423</v>
+        <v>52.36083316755475</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>31.54186323162579</v>
+        <v>22.82188690140239</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3993466292878032</v>
+        <v>0.6223052846870452</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>1</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-3.499207877804229</v>
+        <v>-0.3464260576540445</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>5344</v>
+        <v>5292</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>立衛</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>572.0395783817796</v>
+        <v>595.7453004942604</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>15.8</v>
+        <v>214</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>48.8569816580675</v>
+        <v>44.93416692394028</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.21593116461345</v>
+        <v>20.27714173939226</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2039578381779663</v>
+        <v>1.074530049426034</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0642821887020277</v>
+        <v>-1.433967038141182</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>4966</v>
+        <v>5269</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>564.894594482696</v>
+        <v>585.137180396471</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>675</v>
+        <v>1375</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.36876036713566</v>
+        <v>45.88227392775649</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>25.83571850476552</v>
+        <v>23.14325877542409</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4894594482695969</v>
+        <v>0.5137180396471016</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-26.00918136592214</v>
+        <v>-27.61884407971358</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6112</v>
+        <v>5236</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>凌陽創新</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>563.1306519560544</v>
+        <v>573.9934662928781</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>46.9</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.16623024380056</v>
+        <v>44.50466209376333</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.88383048109636</v>
+        <v>31.54186336784461</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3130651956054344</v>
+        <v>0.3993466292878032</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>1</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.2476430414796052</v>
+        <v>-3.499207878567387</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>5386</v>
+        <v>5344</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>青雲</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>561.3090346267551</v>
+        <v>572.0395783817796</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>485.5</v>
+        <v>15.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.91403199162996</v>
+        <v>48.85698167832259</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>24.33532652038286</v>
+        <v>18.21593120125484</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6309034626755106</v>
+        <v>0.2039578381779663</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-13.35009468898792</v>
+        <v>-0.0642821887592666</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>4972</v>
+        <v>4966</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>湯石照明</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>555.3882150157765</v>
+        <v>564.894594482696</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>16.7</v>
+        <v>675</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.55233474083635</v>
+        <v>43.36876037022103</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>30.78159838603577</v>
+        <v>25.83571852881368</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5388215015776466</v>
+        <v>0.4894594482695969</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0343595526484159</v>
+        <v>-26.00918136763929</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>5269</v>
+        <v>5386</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>青雲</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>555.137180396471</v>
+        <v>561.3090346267551</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1375</v>
+        <v>485.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.88227391809989</v>
+        <v>48.91403199463451</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.14325871887791</v>
+        <v>24.3353267224003</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5137180396471016</v>
+        <v>0.6309034626755106</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-27.61884406826583</v>
+        <v>-13.35009468944583</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6141</v>
+        <v>4972</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>柏承</t>
+          <t>湯石照明</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>548.4787418816486</v>
+        <v>555.3882150157765</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>32.05</v>
+        <v>16.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.46294772103922</v>
+        <v>53.55233493625854</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>21.64594205862552</v>
+        <v>30.78159844070898</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3478741881648625</v>
+        <v>0.5388215015776466</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.265397998607938</v>
+        <v>0.0343595525720977</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>4967</v>
+        <v>4545</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>銘鈺</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>535.6045069542802</v>
+        <v>553.4677351820438</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>272</v>
+        <v>34.85</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.03490526733709</v>
+        <v>47.68900475434731</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>24.1427405358842</v>
+        <v>40.15573849845904</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.06045069542802</v>
+        <v>0.346773518204382</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.375858782564596</v>
+        <v>-0.5437485622627887</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>5215</v>
+        <v>5348</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>529.4645226037039</v>
+        <v>543.526155256616</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>43.05</v>
+        <v>16.45</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.20373260132431</v>
+        <v>53.65872907733642</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>41.98431007221315</v>
+        <v>13.06828649586519</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.446452260370391</v>
+        <v>0.3526155256615949</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.9524575114736636</v>
+        <v>0.3905599304776755</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>5348</v>
+        <v>5481</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>新華</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>528.526155256616</v>
+        <v>529.337056484752</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>16.45</v>
+        <v>19.9</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.65872910932388</v>
+        <v>54.75528321665453</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.06828613608223</v>
+        <v>21.95024280953449</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3526155256615949</v>
+        <v>2.433705648475202</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3905599303441202</v>
+        <v>0.2041339238089478</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>5469</v>
+        <v>4554</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>瀚宇博</t>
+          <t>橙的</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>528.3277238319336</v>
+        <v>528.1753232336246</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>83.7</v>
+        <v>29.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.92619351328812</v>
+        <v>44.77793074425094</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>15.59166992177795</v>
+        <v>25.3803617617362</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.8327723831933548</v>
+        <v>0.3175323233624519</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0993948457291816</v>
+        <v>-0.1239445240812062</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>4554</v>
+        <v>6112</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>橙的</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>528.1753232336246</v>
+        <v>523.1306519560544</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>29.9</v>
+        <v>46.9</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>44.77793052695048</v>
+        <v>53.16623026136401</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>25.38036173340257</v>
+        <v>21.88383059250733</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3175323233624519</v>
+        <v>0.3130651956054344</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,51 +4704,51 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.123944523880871</v>
+        <v>0.2476430411552549</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>4545</v>
+        <v>4945</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>銘鈺</t>
+          <t>陞達科技</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>523.4677351820438</v>
+        <v>514.2651276632713</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>34.85</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="G81" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.68900472547354</v>
+        <v>54.10394125836282</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>40.15573835292614</v>
+        <v>13.02867371601864</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.346773518204382</v>
+        <v>0.4265127663271301</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.5437485620910791</v>
+        <v>0.5430850491513864</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>5481</v>
+        <v>5220</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>新華</t>
+          <t>萬達光電</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>514.337056484752</v>
+        <v>514.1356844874605</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>19.9</v>
+        <v>21.2</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.75540310790041</v>
+        <v>42.26354978064329</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.95030313774446</v>
+        <v>32.99302768721343</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.433705648475202</v>
+        <v>0.4135684487460455</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.2041338852280427</v>
+        <v>-0.349730453287033</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>5220</v>
+        <v>4909</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>萬達光電</t>
+          <t>新復興</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>514.1356844874605</v>
+        <v>511.3087005742129</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>21.2</v>
+        <v>49.2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.26354982955014</v>
+        <v>40.4542851607837</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>32.99302772434492</v>
+        <v>29.77859627413155</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4135684487460455</v>
+        <v>0.6308700574212894</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.3497304532488732</v>
+        <v>-0.2902109240088677</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>4909</v>
+        <v>4967</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>新復興</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>511.3087005742129</v>
+        <v>510.6045069542802</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>49.2</v>
+        <v>272</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.45428507773951</v>
+        <v>48.03490525976355</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>29.77859630697737</v>
+        <v>24.14274057371276</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6308700574212894</v>
+        <v>1.06045069542802</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.2902109230739769</v>
+        <v>-2.375858782869857</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6103</v>
+        <v>6141</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>合邦</t>
+          <t>柏承</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>501.4479576604695</v>
+        <v>508.4787418816486</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>36.5</v>
+        <v>32.05</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>52.38244529621462</v>
+        <v>43.46294772629767</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>9.34081658314755</v>
+        <v>21.64594227137776</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.144795766046953</v>
+        <v>0.3478741881648625</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,51 +4969,51 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.3462524253031391</v>
+        <v>-1.265397998676619</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>4945</v>
+        <v>6103</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>陞達科技</t>
+          <t>合邦</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>499.2651276632713</v>
+        <v>501.4479576604695</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G86" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>54.06204532545198</v>
+        <v>52.38244529299051</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.95316206891838</v>
+        <v>9.340816624430831</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4265127663271301</v>
+        <v>1.144795766046953</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.5436953806723859</v>
+        <v>-0.3462524251123422</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>5245</v>
+        <v>5469</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>497.203721529305</v>
+        <v>498.3277238319336</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>26</v>
+        <v>83.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.92309005788988</v>
+        <v>49.92619355638795</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>32.01672964434527</v>
+        <v>15.59167011269384</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.220372152930496</v>
+        <v>0.8327723831933548</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2147440126897084</v>
+        <v>-0.0993948460344508</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>4908</v>
+        <v>5245</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>494.9281976804688</v>
+        <v>497.203721529305</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>199</v>
+        <v>26</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.18489686543674</v>
+        <v>46.92309015176546</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>29.60112126425591</v>
+        <v>32.01672967697889</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4928197680468831</v>
+        <v>0.220372152930496</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-8.858830988157951</v>
+        <v>-0.2147440128518831</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>4989</v>
+        <v>4908</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>493.4311159077796</v>
+        <v>494.9281976804688</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>79.7</v>
+        <v>199</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>36.30422308508054</v>
+        <v>43.18489687654402</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>24.81274035157984</v>
+        <v>29.60112143777632</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3431115907779585</v>
+        <v>0.4928197680468831</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-2.593843840321161</v>
+        <v>-8.858830988711304</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>5460</v>
+        <v>5215</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>487.2055259867439</v>
+        <v>489.4645226037039</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>14.85</v>
+        <v>43.05</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.29790904239754</v>
+        <v>44.20373260132431</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>32.81744395174373</v>
+        <v>41.98431019707663</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.2205525986743828</v>
+        <v>0.446452260370391</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0490626348262152</v>
+        <v>-0.95245751158814</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>5230</v>
+        <v>5460</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>同協</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>481.8807304219759</v>
+        <v>487.2055259867439</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17.55</v>
+        <v>14.85</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.8674234144731</v>
+        <v>46.29790891639395</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.68668966513787</v>
+        <v>32.81744388630528</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6880730421975907</v>
+        <v>0.2205525986743828</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0055506962284235</v>
+        <v>-0.0490626348166747</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>5388</v>
+        <v>5230</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>中磊</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>481.5000003431655</v>
+        <v>481.8807304219759</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>85.3</v>
+        <v>17.55</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>50.82652708800995</v>
+        <v>51.86742350681654</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.23106117546221</v>
+        <v>15.6866898067684</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6500000343165482</v>
+        <v>0.6880730421975907</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.4524918668871438</v>
+        <v>0.005550696133025</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>4582</v>
+        <v>5432</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>聚恆-創</t>
+          <t>新門</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>478.3706005034173</v>
+        <v>476.0478603232383</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.14934306183675</v>
+        <v>47.76378615548153</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.48941450791729</v>
+        <v>14.71119883992355</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3370600503417259</v>
+        <v>1.10478603232383</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.2488022375288858</v>
+        <v>0.0764733929372001</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>5432</v>
+        <v>4935</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>新門</t>
+          <t>茂林-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>476.0478603232383</v>
+        <v>462.790906562877</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.76378612073766</v>
+        <v>52.90822002356309</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.71119874435002</v>
+        <v>19.7163394702323</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.10478603232383</v>
+        <v>0.7790906562877012</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,11 +5446,11 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0764733941773956</v>
+        <v>-0.173730979488786</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.26707241598718</v>
+        <v>46.26707237248365</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9.178928579478852</v>
+        <v>9.17892869329993</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.4400841169293892</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3416014733270523</v>
+        <v>-0.3416014732793587</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>4588</v>
+        <v>6125</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>玖鼎電力</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>445.7358382968737</v>
+        <v>454.1545178611753</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>58.4</v>
+        <v>60.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.85465140575012</v>
+        <v>46.0156850846289</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.64131285003308</v>
+        <v>28.799724595307</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5735838296873759</v>
+        <v>0.4154517861175307</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.106448342511927</v>
+        <v>-1.027849764782501</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>5251</v>
+        <v>4582</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>天鉞電</t>
+          <t>聚恆-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>440.1805728295361</v>
+        <v>453.3706005034173</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>53.0209614885732</v>
+        <v>43.1493430966529</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>31.78084934632783</v>
+        <v>16.48941476231083</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5180572829536138</v>
+        <v>0.3370600503417259</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1404437725679702</v>
+        <v>0.2488022373285514</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>4942</v>
+        <v>4989</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>榮科</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>436.2221647474671</v>
+        <v>443.4311159077796</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>37.5</v>
+        <v>79.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.89466066887058</v>
+        <v>36.30422308760483</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.43283629967653</v>
+        <v>24.81274047410124</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6222164747467028</v>
+        <v>0.3431115907779585</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0522800383860787</v>
+        <v>-2.593843840407009</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>4933</v>
+        <v>5388</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>中磊</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>433.2111134969527</v>
+        <v>441.5000003431655</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>67.5</v>
+        <v>85.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.93504604122381</v>
+        <v>50.82652712137247</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>29.13103028385489</v>
+        <v>18.23106121493302</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3211113496952685</v>
+        <v>0.6500000343165482</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.384433411876419</v>
+        <v>-0.4524918669443876</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>4935</v>
+        <v>5251</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>茂林-KY</t>
+          <t>天鉞電</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>432.790906562877</v>
+        <v>440.1805728295361</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.90821998916894</v>
+        <v>53.02096140782264</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>19.71633935016716</v>
+        <v>31.78084958352344</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7790906562877012</v>
+        <v>0.5180572829536138</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1737309793075333</v>
+        <v>0.1404437725775097</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>4577</v>
+        <v>4942</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>嘉彰</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>430.0778767432003</v>
+        <v>436.2221647474671</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>85.7</v>
+        <v>37.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>27.02750430194277</v>
+        <v>45.89466071798967</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>30.74674389023313</v>
+        <v>19.43283636251684</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5077876743200307</v>
+        <v>0.6222164747467028</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-2.676586259662322</v>
+        <v>-0.0522800385291746</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>5234</v>
+        <v>4933</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>達興材料</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>428.3423704499819</v>
+        <v>433.2111134969527</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>390.5</v>
+        <v>67.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,49 +5852,49 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.08605272393412</v>
+        <v>41.93504615124485</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.34084807346662</v>
+        <v>29.13103038207687</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3342370449981871</v>
+        <v>0.3211113496952685</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-3.156208018994852</v>
+        <v>-1.384433412353398</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6152</v>
+        <v>4577</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>百一</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>422.3002276556598</v>
+        <v>430.0778767432003</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>15</v>
+        <v>85.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>47.66495365927798</v>
+        <v>27.02750430757085</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.808664474674501</v>
+        <v>30.74674398140521</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7300227655659792</v>
+        <v>0.5077876743200307</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0285482930274428</v>
+        <v>-2.676586259824498</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>5315</v>
+        <v>6129</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>光聯</t>
+          <t>普誠</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>406.0568513440351</v>
+        <v>421.308316663201</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>22.2</v>
+        <v>15.35</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.26989865334833</v>
+        <v>45.25153817456759</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.12959455765098</v>
+        <v>12.58882840784262</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6056851344035142</v>
+        <v>0.6308316663200948</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>1</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0112584592438035</v>
+        <v>-0.1029793446609051</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>4951</v>
+        <v>5315</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>光聯</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>405.2847830987428</v>
+        <v>406.0568513440351</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>102</v>
+        <v>22.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>39.67014619568074</v>
+        <v>48.26989868880459</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>31.9406553285061</v>
+        <v>13.12959459675287</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5284783098742802</v>
+        <v>0.6056851344035142</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-4.167552256015398</v>
+        <v>0.0112584591770263</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>4949</v>
+        <v>4588</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>有成精密</t>
+          <t>玖鼎電力</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>399.4890677061428</v>
+        <v>405.7358382968737</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>89.40000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.65336369948303</v>
+        <v>50.85465145818026</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.23427122368223</v>
+        <v>20.64131295319732</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4489067706142736</v>
+        <v>0.5735838296873759</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.642040570354985</v>
+        <v>0.1064483422829656</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>5371</v>
+        <v>4951</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>399.465386874614</v>
+        <v>405.2847830987428</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>39.22406091364559</v>
+        <v>39.67014618704256</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.45586139230068</v>
+        <v>31.9406553840035</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4465386874614011</v>
+        <v>0.5284783098742802</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.4677571271398673</v>
+        <v>-4.167552256015398</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6104</v>
+        <v>5371</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>創惟</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>392.7092702343122</v>
+        <v>399.465386874614</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.53291093633133</v>
+        <v>39.22406100442955</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.08207868539883</v>
+        <v>13.45586139701151</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7709270234312292</v>
+        <v>0.4465386874614011</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>1</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.3736080287619996</v>
+        <v>-0.4677571276168542</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6114</v>
+        <v>6104</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>久威</t>
+          <t>創惟</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>390.1445511430402</v>
+        <v>392.7092702343122</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>29.85</v>
+        <v>99</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.31733220858862</v>
+        <v>48.53291125464184</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>34.80452806854896</v>
+        <v>20.0820787559916</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5144551143040198</v>
+        <v>0.7709270234312292</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1146178236758669</v>
+        <v>-0.3736080305745423</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>5258</v>
+        <v>6114</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>久威</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>388.6305665910148</v>
+        <v>390.1445511430402</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>50</v>
+        <v>29.85</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45.19268689865475</v>
+        <v>47.31733177335449</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19.43603127113628</v>
+        <v>34.80452811975651</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3630566591014854</v>
+        <v>0.5144551143040198</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.544520753152002</v>
+        <v>-0.1146178230367041</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>5225</v>
+        <v>5234</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>達興材料</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>379.5668356984891</v>
+        <v>388.3423704499819</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>390.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,49 +6329,49 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.51212914433241</v>
+        <v>44.08605273081545</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>30.50079326725564</v>
+        <v>16.34084818853679</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4566835698489032</v>
+        <v>0.3342370449981871</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M111" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1879464213466228</v>
+        <v>-3.156208020139628</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>4927</v>
+        <v>6152</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>泰鼎-KY</t>
+          <t>百一</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>373.7582047813854</v>
+        <v>382.3002276556598</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>49.5</v>
+        <v>15</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.16917782008058</v>
+        <v>47.66495366735194</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.56569790663952</v>
+        <v>9.808664457563667</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3758204781385392</v>
+        <v>0.7300227655659792</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,11 +6400,11 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.8306947994727629</v>
+        <v>-0.028548293078957</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.29981066428892</v>
+        <v>46.29981066913905</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>31.41045783103135</v>
+        <v>31.41045787283529</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.4211713208786568</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.09641018176354151</v>
+        <v>-0.0964101817921597</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6109</v>
+        <v>4927</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>亞元</t>
+          <t>泰鼎-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>365.7326183396298</v>
+        <v>368.7582047813854</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>11.15</v>
+        <v>49.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.93045914708233</v>
+        <v>44.16917786422194</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.36731562030193</v>
+        <v>19.5656982450463</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.073261833962981</v>
+        <v>0.3758204781385392</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0325730121516326</v>
+        <v>-0.8306947998925078</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>4991</v>
+        <v>6109</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>亞元</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>349.6181356403966</v>
+        <v>365.7326183396298</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>554</v>
+        <v>11.15</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.99235469411448</v>
+        <v>45.93045910954171</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>23.19231655738299</v>
+        <v>14.36731560185196</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.461813564039659</v>
+        <v>1.073261833962981</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,11 +6559,11 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-28.94939844341251</v>
+        <v>0.0325730121745274</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>345.1476379643098</v>
+        <v>365.1476379643098</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>180.5</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.3174002747713</v>
+        <v>44.31740028815837</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>11.18519262040186</v>
+        <v>11.1851926560071</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.5147637964309811</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-4.855714654639317</v>
+        <v>-4.855714655593298</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6142</v>
+        <v>4949</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>友勁</t>
+          <t>有成精密</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>340.9608852682014</v>
+        <v>359.4890677061427</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>8.43</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>48.25929163546327</v>
+        <v>44.65336363933956</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.30597764202759</v>
+        <v>22.2342712196761</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5960885268201385</v>
+        <v>0.4489067706142736</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0300790763912933</v>
+        <v>-1.642040570230958</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6108</v>
+        <v>4991</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>競國</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>339.4500726483375</v>
+        <v>349.6181356403966</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>18.85</v>
+        <v>554</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>47.12764844342899</v>
+        <v>38.99235470449707</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.56976135267035</v>
+        <v>23.19231656108045</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.945007264833754</v>
+        <v>1.461813564039659</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.1858692519171788</v>
+        <v>-28.94939844488146</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>4912</v>
+        <v>5258</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>聯德控股-KY</t>
+          <t>虹堡</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>338.3638846747161</v>
+        <v>348.6305665910148</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>90.8</v>
+        <v>50</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>42.43082725524514</v>
+        <v>45.19268708621723</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>24.92502342042814</v>
+        <v>19.43603139373912</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.3363884674716157</v>
+        <v>0.3630566591014854</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-2.235981295606309</v>
+        <v>-0.5445207538770203</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>5272</v>
+        <v>5487</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>334.9878974125758</v>
+        <v>344.3934352058963</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>21.25</v>
+        <v>27.3</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.62777280725843</v>
+        <v>46.57751854625004</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.83348575020974</v>
+        <v>19.15148116546684</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.9987897412575792</v>
+        <v>2.43934352058963</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1907350396658294</v>
+        <v>0.07082786368240709</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>4749</v>
+        <v>5225</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>新應材</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>334.348654770217</v>
+        <v>339.5668356984891</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>921</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>38.98297679757766</v>
+        <v>44.51212933935345</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.49725259018469</v>
+        <v>30.5007933444707</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.434865477021703</v>
+        <v>0.4566835698489032</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-23.1093052689956</v>
+        <v>0.1879464201827776</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>4903</v>
+        <v>5272</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>333.5339376904035</v>
+        <v>334.9878974125758</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>38.75</v>
+        <v>21.25</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>33.67167406329872</v>
+        <v>42.62777284218198</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>16.0773979505485</v>
+        <v>15.83348591186207</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3533937690403552</v>
+        <v>0.9987897412575792</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.750106626245779</v>
+        <v>-0.1907350398184625</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>5291</v>
+        <v>4749</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>邑昇</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>332.8117418149948</v>
+        <v>334.348654770217</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>65</v>
+        <v>921</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.11258619037733</v>
+        <v>38.98297682679307</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>19.29768416388974</v>
+        <v>19.49725291278212</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.281174181499476</v>
+        <v>0.434865477021703</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.9928280345502692</v>
+        <v>-23.10930527481485</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>5439</v>
+        <v>4903</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>330.2949599974639</v>
+        <v>333.5339376904035</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>327</v>
+        <v>38.75</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>34.61897924876824</v>
+        <v>33.67167411268089</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>18.82911891767076</v>
+        <v>16.07739808034362</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>2.029495999746391</v>
+        <v>0.3533937690403552</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-5.563867484434985</v>
+        <v>-0.750106626474732</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>4971</v>
+        <v>5291</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>IET-KY</t>
+          <t>邑昇</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>329.5057380388998</v>
+        <v>332.8117418149948</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>538</v>
+        <v>65</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>35.09230042870978</v>
+        <v>43.11258619140104</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>16.74911659201114</v>
+        <v>19.29768416821191</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.9505738038899836</v>
+        <v>0.281174181499476</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-24.35434248393561</v>
+        <v>-0.9928280345884248</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>5487</v>
+        <v>5439</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>329.3934352058963</v>
+        <v>330.2949599974639</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>27.3</v>
+        <v>327</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46.57751856888096</v>
+        <v>34.61897928702994</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>19.15148127361289</v>
+        <v>18.82911919543681</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>2.43934352058963</v>
+        <v>2.029495999746391</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.07082786352977059</v>
+        <v>-5.563867486915299</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>5475</v>
+        <v>4971</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>IET-KY</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>328.7536042203955</v>
+        <v>329.5057380388998</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>240</v>
+        <v>538</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>37.16223599903513</v>
+        <v>35.09230042971356</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.72495534648465</v>
+        <v>16.74911668501585</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.3753604220395448</v>
+        <v>0.9505738038899836</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-5.954632579262835</v>
+        <v>-24.35434248612982</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>5392</v>
+        <v>5475</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>322.6609792756174</v>
+        <v>328.7536042203955</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>42.15</v>
+        <v>240</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>47.62360882853704</v>
+        <v>37.1622359988986</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>11.91901456590532</v>
+        <v>19.7249554778824</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.2660979275617407</v>
+        <v>0.3753604220395448</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.4566647207574914</v>
+        <v>-5.954632579320092</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>5465</v>
+        <v>5392</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>富驊</t>
+          <t>能率</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>315.6767597423708</v>
+        <v>322.6609792756174</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>26.1</v>
+        <v>42.15</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>50.08543274728197</v>
+        <v>47.62360889237569</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>26.06863819650856</v>
+        <v>11.91901486552824</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.5676759742370832</v>
+        <v>0.2660979275617407</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.08432314083114741</v>
+        <v>-0.4566647211200088</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>4905</v>
+        <v>5222</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>全訊</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>305.0434691202296</v>
+        <v>322.2603977159832</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>72</v>
+        <v>113.5</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>37.8634283143934</v>
+        <v>32.73015978372078</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.56452880187755</v>
+        <v>21.28121038036633</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.5043469120229527</v>
+        <v>0.7260397715983258</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-1.056263301758553</v>
+        <v>-1.010723866311908</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>5222</v>
+        <v>6142</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>全訊</t>
+          <t>友勁</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>292.2603977159832</v>
+        <v>320.9608852682014</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>113.5</v>
+        <v>8.43</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>32.73015976868813</v>
+        <v>48.25929166460937</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>21.28121025508186</v>
+        <v>18.30597770425216</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.7260397715983258</v>
+        <v>0.5960885268201385</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-1.010723865739538</v>
+        <v>0.030079076364582</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>5244</v>
+        <v>5465</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>弘凱</t>
+          <t>富驊</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>290.2164160670561</v>
+        <v>315.6767597423708</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>37.15</v>
+        <v>26.1</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>41.74247619742008</v>
+        <v>50.08543291024444</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>13.63227420026104</v>
+        <v>26.06863833544388</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.5216416067056141</v>
+        <v>0.5676759742370832</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>1</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.1768115601767659</v>
+        <v>-0.0843231411745806</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>5287</v>
+        <v>4905</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>289.9995807158128</v>
+        <v>305.0434691202296</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>41.72317062492531</v>
+        <v>37.86342839362111</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>18.65750386673741</v>
+        <v>13.56452874551741</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.4999580715812785</v>
+        <v>0.5043469120229527</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.3401517373082079</v>
+        <v>-1.056263302521729</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>5223</v>
+        <v>5287</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>289.387927101592</v>
+        <v>304.9995807158128</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>25.6</v>
+        <v>147</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,16 +7548,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>51.5856439483787</v>
+        <v>41.7231707122323</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>15.57095791964083</v>
+        <v>18.65750395583295</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.4387927101591951</v>
+        <v>0.4999580715812785</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.0389348940001988</v>
+        <v>0.3401517364496205</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>4585</v>
+        <v>6136</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>達明</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>281.9084306452576</v>
+        <v>300.8044339343508</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>304.5</v>
+        <v>25.15</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>38.69234703899414</v>
+        <v>45.66238043948076</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>20.52526844877952</v>
+        <v>12.33424806288428</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.6908430645257635</v>
+        <v>0.5804433934350798</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-6.071100744050153</v>
+        <v>-0.1226219900197086</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>6136</v>
+        <v>6108</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>富爾特</t>
+          <t>競國</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>270.8044339343508</v>
+        <v>299.4500726483375</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>25.15</v>
+        <v>18.85</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,16 +7654,16 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45.66238033392693</v>
+        <v>47.12764844342899</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>12.33424814666033</v>
+        <v>16.56976137368585</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.5804433934350798</v>
+        <v>0.945007264833754</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.1226219900483288</v>
+        <v>-0.1858692519457967</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>5340</v>
+        <v>4912</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>聯德控股-KY</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>255.6134523807883</v>
+        <v>298.3638846747161</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>89.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>35.98272993594112</v>
+        <v>42.4308272940759</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>16.08321449267812</v>
+        <v>24.92502368695381</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.5613452380788279</v>
+        <v>0.3363884674716157</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-1.288042453246776</v>
+        <v>-2.235981296369491</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>4968</v>
+        <v>5223</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>立積</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>255.2418556158977</v>
+        <v>289.387927101592</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>107</v>
+        <v>25.6</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>40.62063447846042</v>
+        <v>51.58564392490891</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>16.95973042182942</v>
+        <v>15.57095803007256</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.5241855615897665</v>
+        <v>0.4387927101591951</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,11 +7778,11 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-1.362597354104809</v>
+        <v>0.0389348939238838</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>253.9956178645705</v>
+        <v>283.9956178645705</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>13.65</v>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>46.53557348978856</v>
+        <v>46.5355735201553</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>16.95414369489823</v>
+        <v>16.95414381465028</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.3995617864570469</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.1708515213018374</v>
+        <v>-0.1708515213672367</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>6118</v>
+        <v>5340</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>建達</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>230.3120394902466</v>
+        <v>255.6134523807883</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>16.95</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>43.51275805546061</v>
+        <v>35.98272993837413</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>23.33431014167761</v>
+        <v>16.08321462612544</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.5312039490246692</v>
+        <v>0.5613452380788279</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.1585316856150956</v>
+        <v>-1.288042453380335</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>4956</v>
+        <v>5244</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>弘凱</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>224.6391976568524</v>
+        <v>250.2164160670561</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>37.4</v>
+        <v>37.15</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,16 +7919,16 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>35.44253583493517</v>
+        <v>41.74247635281944</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>19.92088223270231</v>
+        <v>13.63227448650411</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.4639197656852444</v>
+        <v>0.5216416067056141</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-1.097169863514312</v>
+        <v>-0.1768115604724991</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>5438</v>
+        <v>4585</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>東友</t>
+          <t>達明</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>220.5204306052775</v>
+        <v>241.9084306452576</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>18.7</v>
+        <v>304.5</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,16 +7972,16 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>42.24581749818434</v>
+        <v>38.69234700791152</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>20.87737562833909</v>
+        <v>20.52526844877952</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.5520430605277488</v>
+        <v>0.6908430645257635</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.0612454291933183</v>
+        <v>-6.071100743859365</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>4960</v>
+        <v>4968</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>立積</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>214.9385935300701</v>
+        <v>235.2418556158977</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>28.55</v>
+        <v>107</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,16 +8025,16 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>37.11010862598153</v>
+        <v>40.62063461626029</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>17.53981282949695</v>
+        <v>16.95973048243374</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.4938593530070067</v>
+        <v>0.5241855615897665</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.6381997460178881</v>
+        <v>-1.362597355821961</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>6117</v>
+        <v>6118</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>迎廣</t>
+          <t>建達</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>212.4138387947114</v>
+        <v>230.3120394902466</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>76.3</v>
+        <v>16.95</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,16 +8078,16 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>39.74048670084502</v>
+        <v>43.51275810408148</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>18.01281649106993</v>
+        <v>23.33431022491968</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.2413838794711429</v>
+        <v>0.5312039490246692</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-1.330470411148057</v>
+        <v>-0.1585316856914157</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>4994</v>
+        <v>5438</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>東友</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>207.7253023578754</v>
+        <v>220.5204306052775</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>87.09999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,16 +8131,16 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>40.92976597186588</v>
+        <v>42.2458176196632</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>19.53873283787864</v>
+        <v>20.87737575935148</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.2725302357875379</v>
+        <v>0.5520430605277488</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.0074684021027504</v>
+        <v>-0.0612454293173301</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>5314</v>
+        <v>4960</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>世紀*</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>195.5312480922475</v>
+        <v>214.9385935300701</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>58.4</v>
+        <v>28.55</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,16 +8184,16 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>44.10826916560084</v>
+        <v>37.11010863707673</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>6.483935793607991</v>
+        <v>17.53981286585632</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.5531248092247485</v>
+        <v>0.4938593530070067</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.0612726468158149</v>
+        <v>-0.6381997460560471</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>5443</v>
+        <v>4956</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>均豪</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>183.3906999797113</v>
+        <v>214.6391976568524</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>102</v>
+        <v>37.4</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>34.93626541249348</v>
+        <v>35.44253588147066</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>19.84909430653297</v>
+        <v>19.92088233696993</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.3390699979711344</v>
+        <v>0.4639197656852444</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-2.952273421020977</v>
+        <v>-1.097169863810037</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8265,52 +8265,264 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
+        <v>6117</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>迎廣</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>212.4138387947114</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>39.74048681412408</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>18.01281654717281</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>0.2413838794711429</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>-1.330470411777674</v>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>4994</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>傳奇</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>207.7253023578754</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>40.92976589632354</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>19.5387327827342</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>0.2725302357875379</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>-0.0074684018165429</v>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>世紀*</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>195.5312480922475</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>44.10826919474258</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>6.483935850649126</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.5531248092247485</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>-0.0612726479033565</v>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>5443</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>均豪</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>183.3906999797113</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>34.93626547780633</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>19.8490945161217</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>0.3390699979711344</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>-2.952273421574279</v>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
         <v>4999</v>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>鑫禾</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D148" s="2" t="n">
-        <v>134.0394609146001</v>
-      </c>
-      <c r="E148" s="2" t="n">
+      <c r="C152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>164.0394609146001</v>
+      </c>
+      <c r="E152" s="2" t="n">
         <v>20.45</v>
       </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>46.57954497904213</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>19.79978762912368</v>
-      </c>
-      <c r="J148" s="2" t="n">
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>46.57954501092901</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>19.79978763676426</v>
+      </c>
+      <c r="J152" s="2" t="n">
         <v>0.4039460914600131</v>
       </c>
-      <c r="K148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N148" s="2" t="n">
-        <v>0.0297936639315412</v>
-      </c>
-      <c r="O148" s="2" t="inlineStr">
+      <c r="K152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>0.0297936638266032</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
